--- a/assets/templates/Plantilla_Carga_Inventario_SercoRiego.xlsx
+++ b/assets/templates/Plantilla_Carga_Inventario_SercoRiego.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CARGA_INVENTARIO" sheetId="1" r:id="Rb5ac993db4e34beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" r:id="R35bf8815cce44a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CARGA_INVENTARIO" sheetId="1" r:id="R2190b0c4676940eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" r:id="Rcf93ded9f0494281"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -59,6 +59,11 @@
         <x:fgColor rgb="FFE9F8EF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B1220"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -67,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="42">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -143,6 +148,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -360,31 +377,39 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="40" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="16" t="str">
+      <x:c r="A1" s="37" t="str">
         <x:v>CODIGO</x:v>
       </x:c>
-      <x:c r="B1" s="17" t="str">
+      <x:c r="B1" s="38" t="str">
         <x:v>DESCRIPCION</x:v>
       </x:c>
-      <x:c r="C1" s="17" t="str">
+      <x:c r="C1" s="38" t="str">
         <x:v>CANTIDAD</x:v>
       </x:c>
-      <x:c r="D1" s="17" t="str">
+      <x:c r="D1" s="38" t="str">
         <x:v>UBICACION</x:v>
       </x:c>
-      <x:c r="E1" s="17" t="str">
-        <x:v>FAMILIA</x:v>
+      <x:c r="E1" s="38" t="str">
+        <x:v>TIPO</x:v>
       </x:c>
-      <x:c r="F1" s="17" t="str">
+      <x:c r="F1" s="38" t="str">
+        <x:v>CATEGORIA</x:v>
+      </x:c>
+      <x:c r="G1" s="40" t="str">
+        <x:v>SUBCATEGORIA</x:v>
+      </x:c>
+      <x:c r="H1" s="40" t="str">
         <x:v>ROTACION</x:v>
       </x:c>
     </x:row>
@@ -405,6 +430,12 @@
         <x:v>PE</x:v>
       </x:c>
       <x:c r="F2" s="19" t="str">
+        <x:v>Conexiones</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>Enlaces</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
         <x:v>MEDIA</x:v>
       </x:c>
     </x:row>
@@ -425,6 +456,12 @@
         <x:v>PVC</x:v>
       </x:c>
       <x:c r="F3" s="19" t="str">
+        <x:v>Válvulas</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>Válvula de pie</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
         <x:v>MEDIA</x:v>
       </x:c>
     </x:row>
@@ -445,6 +482,12 @@
         <x:v>PVC</x:v>
       </x:c>
       <x:c r="F4" s="19" t="str">
+        <x:v>Conexiones</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>Salida estanque</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
         <x:v>ALTA</x:v>
       </x:c>
     </x:row>
@@ -9217,14 +9260,17 @@
       <x:c r="C2000" s="14"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="F2:F2000">
+      <x:formula1>"ALTA,MEDIA,BAJA"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H2:H5000">
       <x:formula1>"ALTA,MEDIA,BAJA"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6f93e437a464ea7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re64ddba40e1d4dc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9233,102 +9279,118 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="34" t="str">
-        <x:v>PLANTILLA DE CARGA MASIVA · SERCO RIEGO WMS</x:v>
+      <x:c r="A1" s="41" t="str">
+        <x:v>PLANTILLA OFICIAL · SERCO RIEGO WMS</x:v>
       </x:c>
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="41" t="str"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="35" t="str">
-        <x:v>Regla</x:v>
+        <x:v>Objetivo</x:v>
       </x:c>
       <x:c r="B2" s="35" t="str">
-        <x:v>Detalle</x:v>
+        <x:v>Carga masiva de productos e inventario sin registrar producto por producto.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="19" t="str">
-        <x:v>1</x:v>
+        <x:v>CODIGO</x:v>
       </x:c>
       <x:c r="B3" s="19" t="str">
-        <x:v>Una fila representa un producto en una ubicación.</x:v>
+        <x:v>Obligatorio. Solo números corridos. Ejemplo: 161550. No usar guiones ni espacios.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="19" t="str">
-        <x:v>2</x:v>
+        <x:v>DESCRIPCION</x:v>
       </x:c>
       <x:c r="B4" s="19" t="str">
-        <x:v>CODIGO es obligatorio y debe contener solamente números, sin guiones ni espacios.</x:v>
+        <x:v>Obligatorio. Nombre o descripción completa del producto.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="19" t="str">
-        <x:v>3</x:v>
+        <x:v>CANTIDAD</x:v>
       </x:c>
       <x:c r="B5" s="19" t="str">
-        <x:v>DESCRIPCION es obligatoria.</x:v>
+        <x:v>Obligatorio. Número entero igual o mayor a 0.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="19" t="str">
-        <x:v>4</x:v>
+        <x:v>UBICACION</x:v>
       </x:c>
       <x:c r="B6" s="19" t="str">
-        <x:v>CANTIDAD es obligatoria, debe ser un número entero igual o mayor a 0.</x:v>
+        <x:v>Obligatorio. Palet o ubicación actual. Ejemplo: BT1, Y, R1.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="19" t="str">
-        <x:v>5</x:v>
+        <x:v>TIPO</x:v>
       </x:c>
       <x:c r="B7" s="19" t="str">
-        <x:v>UBICACION es obligatoria. Ejemplos: BT1, Y, T, RACKA1, REPISA20.</x:v>
+        <x:v>Opcional. Clasificación general. Ejemplo: PVC, PPR, Orbit, PE.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="19" t="str">
-        <x:v>6</x:v>
+        <x:v>CATEGORIA</x:v>
       </x:c>
       <x:c r="B8" s="19" t="str">
-        <x:v>FAMILIA es opcional. Si queda vacía, el WMS usará “Inventario importado”.</x:v>
+        <x:v>Opcional. Grupo funcional. Ejemplo: Conexiones, Válvulas, Riego.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="19" t="str">
-        <x:v>7</x:v>
+        <x:v>SUBCATEGORIA</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>ROTACION es opcional: ALTA, MEDIA o BAJA. Si queda vacía, se usará MEDIA.</x:v>
+        <x:v>Opcional. Clasificación más específica. Ejemplo: Codos, Enlaces, Válvula de pie.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="19" t="str">
-        <x:v>8</x:v>
+        <x:v>ROTACION</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>Un mismo CODIGO puede repetirse en varias filas si existe en más de una ubicación.</x:v>
+        <x:v>Opcional. Valores permitidos: ALTA, MEDIA o BAJA.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="19" t="str">
-        <x:v>9</x:v>
+        <x:v>Regla de filas</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>No agregues columnas de Foto. El importador no las necesita.</x:v>
+        <x:v>Una fila representa un producto en una ubicación. Si el mismo código está en dos ubicaciones, usar dos filas.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="19" t="str">
-        <x:v>10</x:v>
+        <x:v>Duplicados</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>Puedes copiar y pegar tus datos debajo de los encabezados. No cambies los nombres de las columnas obligatorias.</x:v>
+        <x:v>Si el mismo código y la misma ubicación aparecen varias veces, el WMS consolida las cantidades durante la validación.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="19" t="str">
+        <x:v>Antes de importar</x:v>
+      </x:c>
+      <x:c r="B13" s="19" t="str">
+        <x:v>El WMS mostrará una vista previa y los errores antes de modificar el inventario.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="19" t="str">
+        <x:v>Importante</x:v>
+      </x:c>
+      <x:c r="B14" s="19" t="str">
+        <x:v>No existe columna Foto. La estructura Tipo / Categoría / Subcategoría reemplaza la clasificación anterior.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
